--- a/downloads/processed_template_data.xlsx
+++ b/downloads/processed_template_data.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 13:14:55</t>
+          <t>2026-03-03 05:31:55</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 13:14:55</t>
+          <t>2026-03-03 05:31:55</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 13:14:55</t>
+          <t>2026-03-03 05:31:55</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 13:14:55</t>
+          <t>2026-03-03 05:31:55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 13:14:55</t>
+          <t>2026-03-03 05:31:55</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
